--- a/artifacts/traceability_reports/drs_vs_srs.xlsx
+++ b/artifacts/traceability_reports/drs_vs_srs.xlsx
@@ -2711,7 +2711,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05T14:20:58+00:00</t>
+          <t>2026-10-06T15:07:44+00:00</t>
         </is>
       </c>
     </row>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>C:\Users\iannuzza\LOCAL_PROJ\Github_copilot_proj\STBIO_AI\data\canonical\canonical_store.sqlite</t>
+          <t>C:\Users\iannuzza\LOCAL_PROJ\Github_copilot_proj\Deterministic_Reqs_workflow\data\canonical\canonical_store.sqlite</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>C:\Users\iannuzza\LOCAL_PROJ\Github_copilot_proj\STBIO_AI\artifacts\traceability_reports\drs_vs_srs.xlsx</t>
+          <t>C:\Users\iannuzza\LOCAL_PROJ\Github_copilot_proj\Deterministic_Reqs_workflow\artifacts\traceability_reports\drs_vs_srs.xlsx</t>
         </is>
       </c>
     </row>

--- a/artifacts/traceability_reports/drs_vs_srs.xlsx
+++ b/artifacts/traceability_reports/drs_vs_srs.xlsx
@@ -2711,7 +2711,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T15:07:44+00:00</t>
+          <t>2026-10-09T15:20:00+00:00</t>
         </is>
       </c>
     </row>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>snap-b2e8101b00dc6909feaed885</t>
+          <t>snap-73c872b1307b6adb5eaf843e</t>
         </is>
       </c>
     </row>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>b2e8101b00dc6909feaed8858c8391a595fd7fe52538e9b17b233477d99c8a6d</t>
+          <t>0c71eaa9e10d8478c2ac3726113d42cead2cf039a4bd64b4fab7e6c9dc116eac</t>
         </is>
       </c>
     </row>

--- a/artifacts/traceability_reports/drs_vs_srs.xlsx
+++ b/artifacts/traceability_reports/drs_vs_srs.xlsx
@@ -9,9 +9,13 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DRS vs SRS" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report Metadata" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Upstream Coverage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirement Presence" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'DRS vs SRS'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Upstream Coverage'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Requirement Presence'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +23,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0&quot;%&quot;"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -62,7 +68,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -72,6 +78,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -161,6 +168,52 @@
     <tableColumn id="7" name="downstream_req_id"/>
     <tableColumn id="8" name="traceability_status"/>
     <tableColumn id="9" name="owning_block"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ReportData2" displayName="ReportData2" ref="A1:P2" headerRowCount="1">
+  <autoFilter ref="A1:P2"/>
+  <tableColumns count="16">
+    <tableColumn id="1" name="covering_level"/>
+    <tableColumn id="2" name="covering_block"/>
+    <tableColumn id="3" name="covered_upstream_level"/>
+    <tableColumn id="4" name="covered_upstream_block"/>
+    <tableColumn id="5" name="denominator_scope"/>
+    <tableColumn id="6" name="covered_unique_upstream_requirements"/>
+    <tableColumn id="7" name="total_unique_upstream_requirements"/>
+    <tableColumn id="8" name="uncovered_upstream_requirements"/>
+    <tableColumn id="9" name="coverage_percentage"/>
+    <tableColumn id="10" name="coverage_status"/>
+    <tableColumn id="11" name="coverage_basis"/>
+    <tableColumn id="12" name="covered_upstream_requirement_ids"/>
+    <tableColumn id="13" name="uncovered_upstream_requirement_ids"/>
+    <tableColumn id="14" name="snapshot_id"/>
+    <tableColumn id="15" name="covering_node_id"/>
+    <tableColumn id="16" name="covered_upstream_node_id"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="ReportData3" displayName="ReportData3" ref="A1:L8" headerRowCount="1">
+  <autoFilter ref="A1:L8"/>
+  <tableColumns count="12">
+    <tableColumn id="1" name="hierarchy_level"/>
+    <tableColumn id="2" name="block"/>
+    <tableColumn id="3" name="scope"/>
+    <tableColumn id="4" name="expected_requirements"/>
+    <tableColumn id="5" name="represented_requirements"/>
+    <tableColumn id="6" name="missing_requirements"/>
+    <tableColumn id="7" name="presence_percentage"/>
+    <tableColumn id="8" name="presence_status"/>
+    <tableColumn id="9" name="coverage_basis"/>
+    <tableColumn id="10" name="missing_requirement_ids"/>
+    <tableColumn id="11" name="snapshot_id"/>
+    <tableColumn id="12" name="reported_block_label_differences"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2711,7 +2764,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T15:20:00+00:00</t>
+          <t>2026-10-15T20:02:15+00:00</t>
         </is>
       </c>
     </row>
@@ -2800,4 +2853,624 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:P2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="33" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="31" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="26" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>covering_level</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>covering_block</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>covered_upstream_level</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>covered_upstream_block</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>denominator_scope</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>covered_unique_upstream_requirements</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>total_unique_upstream_requirements</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>uncovered_upstream_requirements</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_percentage</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_status</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_basis</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>covered_upstream_requirement_ids</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>uncovered_upstream_requirement_ids</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>snapshot_id</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>covering_node_id</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>covered_upstream_node_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DRS</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>(All blocks)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Primary source specification: dds_stbio1.pdf</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>(All blocks)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Approved source ledger</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>55</v>
+      </c>
+      <c r="G2" t="n">
+        <v>357</v>
+      </c>
+      <c r="H2" t="n">
+        <v>302</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>15.40616246498599</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Unique upstream IDs resolved by central approved Covers contract; not publication gate status</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>DDS_STBIO1_0032;DDS_STBIO1_0036;DDS_STBIO1_0116;DDS_STBIO1_0141;DDS_STBIO1_0142;DDS_STBIO1_0143;DDS_STBIO1_0144;DDS_STBIO1_0145;DDS_STBIO1_0146;DDS_STBIO1_0147;DDS_STBIO1_0148;DDS_STBIO1_0149;DDS_STBIO1_0201;DDS_STBIO1_0202;DDS_STBIO1_0203;DDS_STBIO1_0204;DDS_STBIO1_0206;DDS_STBIO1_0207;DDS_STBIO1_0208;DDS_STBIO1_0209;DDS_STBIO1_0210;DDS_STBIO1_0211;DDS_STBIO1_0212;DDS_STBIO1_0213;DDS_STBIO1_0215;DDS_STBIO1_0216;DDS_STBIO1_0217;DDS_STBIO1_0218;DDS_STBIO1_0219;DDS_STBIO1_0220;DDS_STBIO1_0221;DDS_STBIO1_0222;DDS_STBIO1_0223;DDS_STBIO1_0501;DDS_STBIO1_05010;DDS_STBIO1_05011;DDS_STBIO1_0502;DDS_STBIO1_0503;DDS_STBIO1_0504;DDS_STBIO1_0505;DDS_STBIO1_0507;DDS_STBIO1_0508;DDS_STBIO1_0509;DDS_STBIO1_0699;DDS_STBIO1_0700;DDS_STBIO1_0701;DDS_STBIO1_0702;DDS_STBIO1_1114;DDS_STBIO1_1507;DDS_STBIO1_2507;DDS_STBIO1_9004;DDS_STBIO1_9011;DDS_STBIO1_9012;DDS_STBIO1_9013;DDS_STBIO1_9014</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>DDS_STBIO1_00000008;DDS_STBIO1_00000102;DDS_STBIO1_00000199;DDS_STBIO1_00000202;DDS_STBIO1_00001199;DDS_STBIO1_0013;DDS_STBIO1_0014;DDS_STBIO1_0015;DDS_STBIO1_0016;DDS_STBIO1_0017;DDS_STBIO1_0018;DDS_STBIO1_0019;DDS_STBIO1_0020;DDS_STBIO1_0021;DDS_STBIO1_0022;DDS_STBIO1_0023;DDS_STBIO1_0024;DDS_STBIO1_0025;DDS_STBIO1_0026;DDS_STBIO1_0027;DDS_STBIO1_0028;DDS_STBIO1_0033;DDS_STBIO1_0034;DDS_STBIO1_0035;DDS_STBIO1_0104;DDS_STBIO1_0105;DDS_STBIO1_0106;DDS_STBIO1_0107;DDS_STBIO1_0108;DDS_STBIO1_0109;DDS_STBIO1_0110;DDS_STBIO1_0111;DDS_STBIO1_0112;DDS_STBIO1_0113;DDS_STBIO1_0114;DDS_STBIO1_0115;DDS_STBIO1_0117;DDS_STBIO1_0118;DDS_STBIO1_0119;DDS_STBIO1_0120;DDS_STBIO1_0121;DDS_STBIO1_0122;DDS_STBIO1_0123;DDS_STBIO1_0124;DDS_STBIO1_0125;DDS_STBIO1_0126;DDS_STBIO1_0127;DDS_STBIO1_0128;DDS_STBIO1_0129;DDS_STBIO1_0130;DDS_STBIO1_0140;DDS_STBIO1_1020;DDS_STBIO1_1021;DDS_STBIO1_1022;DDS_STBIO1_1023;DDS_STBIO1_1024;DDS_STBIO1_1025;DDS_STBIO1_1026;DDS_STBIO1_1027;DDS_STBIO1_1050;DDS_STBIO1_1051;DDS_STBIO1_1052;DDS_STBIO1_1053;DDS_STBIO1_1054;DDS_STBIO1_2024;DDS_STBIO1_2025;DDS_STBIO1_2026;DDS_STBIO1_2052;DDS_STBIO1_2053;DDS_STBIO1_2054;DDS_STBIO1_3000;DDS_STBIO1_3001;DDS_STBIO1_3002;DDS_STBIO1_3003;DDS_STBIO1_3004;DDS_STBIO1_3005;DDS_STBIO1_3006;DDS_STBIO1_302;DDS_STBIO1_303;DDS_STBIO1_304;DDS_STBIO1_305;DDS_STBIO1_306;DDS_STBIO1_307;DDS_STBIO1_308;DDS_STBIO1_309;DDS_STBIO1_310;DDS_STBIO1_311;DDS_STBIO1_312;DDS_STBIO1_313;DDS_STBIO1_314;DDS_STBIO1_392;DDS_STBIO1_393;DDS_STBIO1_394;DDS_STBIO1_395;DDS_STBIO1_4000;DDS_STBIO1_8000;DDS_STBIO1_8001;DDS_STBIO1_8002;DDS_STBIO1_8003;DDS_STBIO1_8004;DDS_STBIO1_8005;DDS_STBIO1_8006;DDS_STBIO1_8007;DDS_STBIO1_8100;DDS_STBIO1_8101;DDS_STBIO1_8102;DDS_STBIO1_8103;DDS_STBIO1_8104;DDS_STBIO1_8105;DDS_STBIO1_8106;DDS_STBIO1_89455232;DDS_STBIO1_89455261;DDS_STBIO1_89455449;DDS_STBIO1_89456557;DDS_STBIO1_89456975;DDS_STBIO1_89457435;DDS_STBIO1_89457790;DDS_STBIO1_89459082;DDS_STBIO1_9017;DDS_STBIO1_9018;DDS_STBIO1_9024;DDS_STBIO1_9027;DDS_STBIO1_9029;DDS_STBIO1_9030;DDS_STBIO1_9031;DDS_STBIO1_9032;DDS_STBIO1_9033;DDS_STBIO1_9034;DDS_STBIO1_9035;DDS_STBIO1_9260;DDS_STBIO1_9261;DDS_STBIO1_9262;DDS_STBIO1_9263;DDS_STBIO1_9300;DDS_STBIO1_9317;DDS_STBIO1_9500;IPOS_STBIO1_MAIN_CONTROLLER_002;IPOS_STBIO1_MAIN_CONTROLLER_004;IPOS_STBIO1_MAIN_CONTROLLER_008;IPOS_STBIO1_MAIN_CONTROLLER_009;IPOS_STBIO1_MAIN_CONTROLLER_010;IPOS_STBIO1_MAIN_CONTROLLER_011;IPOS_STBIO1_MAIN_CONTROLLER_015;IPOS_STBIO1_MAIN_CONTROLLER_0152;IPOS_STBIO1_MAIN_CONTROLLER_016;IPOS_STBIO1_MAIN_CONTROLLER_017;IPOS_STBIO1_MAIN_CONTROLLER_018;IPOS_STBIO1_MAIN_CONTROLLER_019;IPOS_STBIO1_MAIN_CONTROLLER_020;IPOS_STBIO1_MAIN_CONTROLLER_021;IPOS_STBIO1_MAIN_CONTROLLER_022;IPOS_STBIO1_MAIN_CONTROLLER_023;IPOS_STBIO1_MAIN_CONTROLLER_024;IPOS_STBIO1_MAIN_CONTROLLER_026;IPOS_STBIO1_MAIN_CONTROLLER_027;IPOS_STBIO1_MAIN_CONTROLLER_028;IPOS_STBIO1_MAIN_CONTROLLER_029;IPOS_STBIO1_MAIN_CONTROLLER_030;IPOS_STBIO1_MAIN_CONTROLLER_031;IPOS_STBIO1_MAIN_CONTROLLER_032;IPOS_STBIO1_MAIN_CONTROLLER_033;IPOS_STBIO1_MAIN_CONTROLLER_034;IPOS_STBIO1_MAIN_CONTROLLER_035;IPOS_STBIO1_MAIN_CONTROLLER_036;IPOS_STBIO1_MAIN_CONTROLLER_037;IPOS_STBIO1_MAIN_CONTROLLER_038;IPOS_STBIO1_MAIN_CONTROLLER_039;IPOS_STBIO1_MAIN_CONTROLLER_040;IPOS_STBIO1_MAIN_CONTROLLER_043;IPOS_STBIO1_MAIN_CONTROLLER_044;IPOS_STBIO1_MAIN_CONTROLLER_045;IPOS_STBIO1_MAIN_CONTROLLER_047;IPOS_STBIO1_MAIN_CONTROLLER_048;IPOS_STBIO1_MAIN_CONTROLLER_049;IPOS_STBIO1_MAIN_CONTROLLER_051;IPOS_STBIO1_MAIN_CONTROLLER_052;IPOS_STBIO1_MAIN_CONTROLLER_053;IPOS_STBIO1_MAIN_CONTROLLER_054;IPOS_STBIO1_MAIN_CONTROLLER_055;IPOS_STBIO1_MAIN_CONTROLLER_058;IPOS_STBIO1_MAIN_CONTROLLER_059;IPOS_STBIO1_MAIN_CONTROLLER_060;IPOS_STBIO1_MAIN_CONTROLLER_061;IPOS_STBIO1_MAIN_CONTROLLER_062;IPOS_STBIO1_MAIN_CONTROLLER_063;IPOS_STBIO1_MAIN_CONTROLLER_064;IPOS_STBIO1_MAIN_CONTROLLER_072;IPOS_STBIO1_MAIN_CONTROLLER_073;IPOS_STBIO1_MAIN_CONTROLLER_074;IPOS_STBIO1_MAIN_CONTROLLER_075;IPOS_STBIO1_MAIN_CONTROLLER_076;IPOS_STBIO1_MAIN_CONTROLLER_077;IPOS_STBIO1_MAIN_CONTROLLER_078;IPOS_STBIO1_MAIN_CONTROLLER_080;IPOS_STBIO1_MAIN_CONTROLLER_081;IPOS_STBIO1_MAIN_CONTROLLER_082;IPOS_STBIO1_MAIN_CONTROLLER_083;IPOS_STBIO1_MAIN_CONTROLLER_084;IPOS_STBIO1_MAIN_CONTROLLER_085;IPOS_STBIO1_MAIN_CONTROLLER_086;IPOS_STBIO1_MAIN_CONTROLLER_087;IPOS_STBIO1_MAIN_CONTROLLER_088;IPOS_STBIO1_MAIN_CONTROLLER_089;IPOS_STBIO1_MAIN_CONTROLLER_090;IPOS_STBIO1_MAIN_CONTROLLER_092;IPOS_STBIO1_MAIN_CONTROLLER_093;IPOS_STBIO1_MAIN_CONTROLLER_094;IPOS_STBIO1_MAIN_CONTROLLER_095;IPOS_STBIO1_MAIN_CONTROLLER_096;IPOS_STBIO1_MAIN_CONTROLLER_097;IPOS_STBIO1_MAIN_CONTROLLER_098;IPOS_STBIO1_MAIN_CONTROLLER_099;IPOS_STBIO1_MAIN_CONTROLLER_100;IPOS_STBIO1_MAIN_CONTROLLER_1004;IPOS_STBIO1_MAIN_CONTROLLER_1005;IPOS_STBIO1_MAIN_CONTROLLER_1007;IPOS_STBIO1_MAIN_CONTROLLER_1008;IPOS_STBIO1_MAIN_CONTROLLER_1009;IPOS_STBIO1_MAIN_CONTROLLER_101;IPOS_STBIO1_MAIN_CONTROLLER_1010;IPOS_STBIO1_MAIN_CONTROLLER_1011;IPOS_STBIO1_MAIN_CONTROLLER_102;IPOS_STBIO1_MAIN_CONTROLLER_103;IPOS_STBIO1_MAIN_CONTROLLER_1034;IPOS_STBIO1_MAIN_CONTROLLER_104;IPOS_STBIO1_MAIN_CONTROLLER_105;IPOS_STBIO1_MAIN_CONTROLLER_106;IPOS_STBIO1_MAIN_CONTROLLER_107;IPOS_STBIO1_MAIN_CONTROLLER_108;IPOS_STBIO1_MAIN_CONTROLLER_109;IPOS_STBIO1_MAIN_CONTROLLER_1095;IPOS_STBIO1_MAIN_CONTROLLER_110;IPOS_STBIO1_MAIN_CONTROLLER_1102;IPOS_STBIO1_MAIN_CONTROLLER_1104;IPOS_STBIO1_MAIN_CONTROLLER_1105;IPOS_STBIO1_MAIN_CONTROLLER_111;IPOS_STBIO1_MAIN_CONTROLLER_1116;IPOS_STBIO1_MAIN_CONTROLLER_1118;IPOS_STBIO1_MAIN_CONTROLLER_1119;IPOS_STBIO1_MAIN_CONTROLLER_112;IPOS_STBIO1_MAIN_CONTROLLER_113;IPOS_STBIO1_MAIN_CONTROLLER_1136;IPOS_STBIO1_MAIN_CONTROLLER_1139;IPOS_STBIO1_MAIN_CONTROLLER_1143;IPOS_STBIO1_MAIN_CONTROLLER_115;IPOS_STBIO1_MAIN_CONTROLLER_118;IPOS_STBIO1_MAIN_CONTROLLER_120;IPOS_STBIO1_MAIN_CONTROLLER_121;IPOS_STBIO1_MAIN_CONTROLLER_122;IPOS_STBIO1_MAIN_CONTROLLER_123;IPOS_STBIO1_MAIN_CONTROLLER_124;IPOS_STBIO1_MAIN_CONTROLLER_125;IPOS_STBIO1_MAIN_CONTROLLER_126;IPOS_STBIO1_MAIN_CONTROLLER_127;IPOS_STBIO1_MAIN_CONTROLLER_128;IPOS_STBIO1_MAIN_CONTROLLER_129;IPOS_STBIO1_MAIN_CONTROLLER_132;IPOS_STBIO1_MAIN_CONTROLLER_133;IPOS_STBIO1_MAIN_CONTROLLER_134;IPOS_STBIO1_MAIN_CONTROLLER_137;IPOS_STBIO1_MAIN_CONTROLLER_138;IPOS_STBIO1_MAIN_CONTROLLER_139;IPOS_STBIO1_MAIN_CONTROLLER_140;IPOS_STBIO1_MAIN_CONTROLLER_143;IPOS_STBIO1_MAIN_CONTROLLER_2117;IPOS_STBIO1_MAIN_CONTROLLER_2143;IPOS_STBIO1_MAIN_CONTROLLER_2144;IPOS_STBIO1_MAIN_CONTROLLER_2145;IPOS_STBIO1_MAIN_CONTROLLER_2146;IPOS_STBIO1_MAIN_CONTROLLER_300;IPOS_STBIO1_MAIN_CONTROLLER_3124;IPOS_STBIO1_MAIN_CONTROLLER_3125;IPOS_STBIO1_MAIN_CONTROLLER_3126;IPOS_STBIO1_MAIN_CONTROLLER_3127;IPOS_STBIO1_MAIN_CONTROLLER_3128;IPOS_STBIO1_MAIN_CONTROLLER_3129;IPOS_STBIO1_MAIN_CONTROLLER_3130;IPOS_STBIO1_MAIN_CONTROLLER_3131;IPOS_STBIO1_MAIN_CONTROLLER_4034;IPOS_STBIO1_MAIN_CONTROLLER_4079;IPOS_STBIO1_MAIN_CONTROLLER_4080;IPOS_STBIO1_MAIN_CONTROLLER_4090;IPOS_STBIO1_MAIN_CONTROLLER_4091;IPOS_STBIO1_MAIN_CONTROLLER_436;IPOS_STBIO1_MAIN_CONTROLLER_5004;IPOS_STBIO1_MAIN_CONTROLLER_5005;IPOS_STBIO1_MAIN_CONTROLLER_5015;IPOS_STBIO1_MAIN_CONTROLLER_5016;IPOS_STBIO1_MAIN_CONTROLLER_5080;IPOS_STBIO1_MAIN_CONTROLLER_5091;IPOS_STBIO1_MAIN_CONTROLLER_5092;IPOS_STBIO1_MAIN_CONTROLLER_6059;IPOS_STBIO1_MAIN_CONTROLLER_6070;IPOS_STBIO1_MAIN_CONTROLLER_6098;IPOS_STBIO1_MAIN_CONTROLLER_6129;IPOS_STBIO1_MAIN_CONTROLLER_7095;IPOS_STBIO1_MAIN_CONTROLLER_7135;IPOS_STBIO1_MAIN_CONTROLLER_728;IPOS_STBIO1_MAIN_CONTROLLER_8106;IPOS_STBIO1_MAIN_CONTROLLER_8116;IPOS_STBIO1_MAIN_CONTROLLER_9116;IPOS_STBIO1_MAIN_CONTROLLER_9139</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>snap-73c872b1307b6adb5eaf843e</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>DRS</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>source:dds_stbio1.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:L8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="31" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>hierarchy_level</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>block</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>scope</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>expected_requirements</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>represented_requirements</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>missing_requirements</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>presence_percentage</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>presence_status</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_basis</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>missing_requirement_ids</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>snapshot_id</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>reported_block_label_differences</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DRS</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>(All blocks)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Level total</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>55</v>
+      </c>
+      <c r="E2" t="n">
+        <v>55</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>all_present</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Approved allocation IDs represented in target traceability matrix</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>snap-73c872b1307b6adb5eaf843e</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>DRS</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ADSP</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>all_present</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Target matrix IDs grouped by approved block allocation; not publication gate status</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>snap-73c872b1307b6adb5eaf843e</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>DRS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Digital Subsystem</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>42</v>
+      </c>
+      <c r="E4" t="n">
+        <v>42</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>all_present</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Target matrix IDs grouped by approved block allocation; not publication gate status</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>snap-73c872b1307b6adb5eaf843e</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DRS</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Main Controller</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>all_present</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Target matrix IDs grouped by approved block allocation; not publication gate status</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>snap-73c872b1307b6adb5eaf843e</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DRS</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>OTP</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>all_present</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Target matrix IDs grouped by approved block allocation; not publication gate status</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>snap-73c872b1307b6adb5eaf843e</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>DRS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Regmap</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>all_present</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Target matrix IDs grouped by approved block allocation; not publication gate status</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>snap-73c872b1307b6adb5eaf843e</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DRS</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Sensor-Hub</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>all_present</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Target matrix IDs grouped by approved block allocation; not publication gate status</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>snap-73c872b1307b6adb5eaf843e</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>